--- a/Month-1/Day-09/AlMosafer_Drivers_Performance_Dashboard.xlsx
+++ b/Month-1/Day-09/AlMosafer_Drivers_Performance_Dashboard.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data-Analysis-and-AI-85Days\Month-1\Day-9\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data-Analysis-and-AI-85Days\Month-1\Day-09\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFE0F36-03CB-48B8-9959-1F20059EC57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB0E9C0-A180-4693-9884-5E73C6D100CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4D9F94B5-4FB4-4A4D-8118-07356F98972F}"/>
   </bookViews>
@@ -381,49 +381,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -2185,7 +2143,7 @@
     <dataField name="Average Rating" fld="4" subtotal="average" baseField="2" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="27">
+    <format dxfId="13">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -2242,7 +2200,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E34A5BDF-BDCE-4123-8039-586E32E90853}" name="Table3" displayName="Table3" ref="A3:E18" headerRowBorderDxfId="26" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E34A5BDF-BDCE-4123-8039-586E32E90853}" name="Table3" displayName="Table3" ref="A3:E18" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="A3:E18" xr:uid="{E34A5BDF-BDCE-4123-8039-586E32E90853}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1">
@@ -2267,13 +2225,13 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{37A4C905-F65E-4D9E-80BB-32932EC23A6C}" name="DriverID" totalsRowLabel="Total" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{E4C2059E-F160-4798-8B93-BDD3F1ADC9CE}" name="DriverName" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{3A12541F-EF26-4AE6-AECD-A66A043BF56F}" name="City" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{C11C46DB-203F-4210-95C2-8E3B9A4823A5}" name="Rating (VLOOKUP) :" dataDxfId="17" totalsRowDxfId="16">
+    <tableColumn id="1" xr3:uid="{37A4C905-F65E-4D9E-80BB-32932EC23A6C}" name="DriverID" totalsRowLabel="Total" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{E4C2059E-F160-4798-8B93-BDD3F1ADC9CE}" name="DriverName" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{3A12541F-EF26-4AE6-AECD-A66A043BF56F}" name="City" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{C11C46DB-203F-4210-95C2-8E3B9A4823A5}" name="Rating (VLOOKUP) :" dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>_xlfn.IFNA(VLOOKUP(A4,Source_Data!$A$2:$C$15,2,FALSE),"No Rate")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A9692640-7B0F-40D4-8514-EB81AE2AF1AC}" name="Rating (XLOOKUP) :" totalsRowFunction="count" dataDxfId="15" totalsRowDxfId="14">
+    <tableColumn id="6" xr3:uid="{A9692640-7B0F-40D4-8514-EB81AE2AF1AC}" name="Rating (XLOOKUP) :" totalsRowFunction="count" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>_xlfn.IFNA(_xlfn.XLOOKUP(A4,Source_Data!$A$2:$A$15,Source_Data!$B$2:$B$15),"No Rate")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2606,7 +2564,7 @@
     <col min="4" max="5" width="21.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.26953125" customWidth="1"/>
     <col min="7" max="7" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
@@ -3312,23 +3270,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d6bf451c-e3aa-4dd1-b5a6-a95183d31bdf" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C75CCA8C93D93A43A1AC488E2F0D8821" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5345ce98933d9ec1471464f61cd0e19e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d6bf451c-e3aa-4dd1-b5a6-a95183d31bdf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="22654faffaec1724d19dfafa100f8372" ns3:_="">
     <xsd:import namespace="d6bf451c-e3aa-4dd1-b5a6-a95183d31bdf"/>
@@ -3478,31 +3419,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AC1D7C8-B82F-4208-A83D-EBCD484A412F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d6bf451c-e3aa-4dd1-b5a6-a95183d31bdf"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E6F7B04-A9D6-4AE5-9FC5-8EF8E8ACB60D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d6bf451c-e3aa-4dd1-b5a6-a95183d31bdf" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CEF5BAA-57C4-45AA-B470-D9FC978495CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3518,4 +3452,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E6F7B04-A9D6-4AE5-9FC5-8EF8E8ACB60D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AC1D7C8-B82F-4208-A83D-EBCD484A412F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d6bf451c-e3aa-4dd1-b5a6-a95183d31bdf"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>